--- a/docs/VARIABLE_RECTIFICATION.xlsx
+++ b/docs/VARIABLE_RECTIFICATION.xlsx
@@ -509,7 +509,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Status: OPEN-ERIN</t>
+          <t>Status: OPEN-PRICE</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Feels_Exausted (+4 siblings)</t>
+          <t>Feels_Exausted, Low_Physical_Activity, Slow_Walking_Speed, Unintended_Weight_Loss, Week_Grip_Strength</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Feels_Exausted_Value (+4)</t>
+          <t>Feels_Exausted_Value, Low_Physical_Activity_Value, Slow_Walking_Speed_Value, Unintended_Weight_Loss_Value, Week_Grip_Strength_Value</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>OPEN-ERIN</t>
+          <t>OPEN-PRICE</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>OPEN-ERIN</t>
+          <t>OPEN-PRICE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">

--- a/docs/VARIABLE_RECTIFICATION.xlsx
+++ b/docs/VARIABLE_RECTIFICATION.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KEY'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KEY'!$A$1:$B$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Duplicate Concepts'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Type &amp; Encoding'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Quality'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Quality'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Coverage &amp; Cohort'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Traps'!$A$1:$C$13</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -617,29 +617,41 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sheets</t>
+          <t>Flag columns</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Concepts | Type &amp; Encoding | Data Quality | Coverage &amp; Cohort | Traps</t>
+          <t>The merged file carries rt_envelope_flag, rt_INCISE_to_DRESS_neg, rt_RM_START_to_INCISION_neg and rt_RM_START_to_RM_END_neg. All are 1/0, all mark RETAINED values. The pipeline flags questionable timestamps rather than nulling them, so the exclude-or-keep decision stays with the analyst.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate Concepts | Type &amp; Encoding | Data Quality | Coverage &amp; Cohort | Traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Caution</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>This register is the project's accumulated knowledge, not a substitute for inspecting the data. Where a row says VERIFY, the check has NOT been run.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1919,7 +1931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1991,17 +2003,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>52 NEGATIVE values -- dressing timestamp before incision. Max is -1; 75% sit between -6.5 and -1. Concentrated in percutaneous services (46% Neurosurgery, 20% EP/interventional cardiology) where there is no incision or dressing in the surgical sense.</t>
+          <t>52 NEGATIVE values -- dressing timestamp before incision. Max is -1; 75% sit between -6.5 and -1. Concentrated in percutaneous services (46% Neurosurgery, 20% EP/interventional cardiology) where there is no incision or dressing in the surgical sense. A TRUE DURATION between two procedure events, so these are the more likely to be genuine errors.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>PCM-F-13, PCM-F-14, PREP-08</t>
+          <t>PCM-F-13, PCM-F-14, MRG-07, QC-08</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Set to missing at source in Phase 3.</t>
+          <t>CHANGED 2026-08-27: values are now RETAINED and flagged rt_INCISE_to_DRESS_neg = 1, not nulled. Phase 3 nulled them until then. Flagging leaves the exclude-or-keep call to the analyst instead of the pipeline pre-empting it.</t>
         </is>
       </c>
     </row>
@@ -2028,66 +2040,66 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>15 NEGATIVE values. Disjoint from the 52 above, so 67 distinct rows are affected.</t>
+          <t>15 NEGATIVE values, disjoint from the 52 above. BELONGS TO THE rt_RM_START_to_* FAMILY -- and rt_RM_START_to_AN_START_mins in that same family is negative on 50-62% of rows because anesthesia routinely begins before OR entry. The family behaves as OFFSETS from room start, not durations, so a negative here may be MEANINGFUL rather than erroneous.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>PCM-F-13, PREP-08</t>
+          <t>PCM-F-13, MRG-07, QC-08, PCM-D-08</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Set to missing at source in Phase 3.</t>
+          <t>CHANGED 2026-08-27: values RETAINED and flagged rt_RM_START_to_INCISION_neg = 1. Nulling these was inconsistent with PCM-D-08 (flag-dont-null) and rested on a clinical assumption that was never measured. See the VERIFY row below.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>rt_INCISE_to_DRESS_mins / rt_RM_START_to_INCISION_mins</t>
+          <t>rt_RM_START_to_RM_END_mins</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>RESOLVED-KEEP</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9 rows where a sub-interval EXCEEDS the room-occupancy interval containing it (5 + 4). All values POSITIVE and inside the old QC-05 bounds, so a range check cannot see them.</t>
+          <t>No negatives found. Included in the flagging scheme for symmetry -- it is the containment envelope QC-06 tests against.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>PCM-F-15, PCM-D-08, MRG-05</t>
+          <t>MRG-07, QC-08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>FLAGGED, not nulled -- rt_envelope_flag = 1. Each timestamp is individually plausible and nothing identifies which of the three is wrong; nulling would destroy two good values to punish one bad one. QC-06 asserts zero UNFLAGGED violations.</t>
+          <t>Flag rt_RM_START_to_RM_END_neg exists and is expected to be 0 on every row.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>rt_RM_START_to_AN_START_mins</t>
+          <t>rt_RM_START_to_INCISION_mins (are the 15 offsets?)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2097,66 +2109,66 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>22,575 in md3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>NEGATIVE on 50-62% of rows in EVERY source. This is not error -- anesthesia routinely starts before OR entry, in pre-op holding or an induction room. The rt_RM_START_to_* family are OFFSETS from room start, not durations.</t>
+          <t>OPEN QUESTION behind the change above. If the 15 fall in the same percutaneous services as the 52 AND their rt_RM_START_to_AN_START_mins is also negative, they are the same offset phenomenon and were never errors. If they are scattered across ordinary surgical services with a positive AN_START, they are genuine timestamp errors.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>PCM-D-10, PREP-09</t>
+          <t>Raised 2026-08-27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Do NOT null. Anyone computing 'time from room entry to anesthesia start' as a duration gets systematically wrong results on half the cohort. Rename or document prominently.</t>
+          <t>VERIFY against the RAW source (Phase 3 no longer nulls, but check src.master_data_3): pull the 15 rows with Service, CPT_1_Description, rt_RM_START_to_INCISION_mins, rt_RM_START_to_AN_START_mins. Frequency alone does not settle it -- 55% negative is a workflow norm, 0.04% is an anomaly, but an anomaly can still be the same phenomenon in an unusual setting.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>rt_RM_START_to_INDUCTION_mins</t>
+          <t>rt_INCISE_to_DRESS_mins / rt_RM_START_to_INCISION_mins</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>RESOLVED-KEEP</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>29 in md3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Small negative counts, same offset-not-duration reasoning as above.</t>
+          <t>9 rows where a sub-interval EXCEEDS the room-occupancy interval containing it (5 + 4). All values POSITIVE and inside the old QC-05 bounds, so a range check cannot see them.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>PREP-09</t>
+          <t>PCM-F-15, PCM-D-08, MRG-05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Review alongside the AN_START variable. Likely legitimate.</t>
+          <t>FLAGGED, not nulled -- rt_envelope_flag = 1. Each timestamp is individually plausible and nothing identifies which of the three is wrong; nulling would destroy two good values to punish one bad one. QC-06 asserts zero UNFLAGGED violations. The same principle was extended to the negative intervals on 2026-08-27 (MRG-07, QC-08).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>rt_BLOCK_START_TO_BLOCK_END_MINS</t>
+          <t>rt_RM_START_to_AN_START_mins</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2166,34 +2178,34 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22,575 in md3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1 negative value in md1/md2/md3. A true duration -- block end before block start is impossible at any scale.</t>
+          <t>NEGATIVE on 50-62% of rows in EVERY source. This is not error -- anesthesia routinely starts before OR entry, in pre-op holding or an induction room. The rt_RM_START_to_* family are OFFSETS from room start, not durations.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>PREP-09</t>
+          <t>PCM-D-10, PREP-09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Genuine error. Decide whether to null it or report upstream. Only one row.</t>
+          <t>Do NOT null. Anyone computing 'time from room entry to anesthesia start' as a duration gets systematically wrong results on half the cohort. Rename or document prominently.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>rt_ADMIT_to_* family</t>
+          <t>rt_RM_START_to_INDUCTION_mins</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2203,17 +2215,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1-4 each</t>
+          <t>29 in md3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Small negative counts. Plausibly real (a block placed in pre-op before the formal admit timestamp) or plausibly error at these counts.</t>
+          <t>Small negative counts, same offset-not-duration reasoning as above.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -2223,123 +2235,197 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Review the PREP-09 report. Low volume either way.</t>
+          <t>Review alongside the AN_START variable. Likely legitimate.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>rt_ANCHOR_to_ADMIT_days etc.</t>
+          <t>rt_BLOCK_START_TO_BLOCK_END_MINS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>RESOLVED-KEEP</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Zero negatives found. These are offsets from an anchor date where negative would be LEGITIMATE.</t>
+          <t>1 negative value in md1/md2/md3. A true duration -- block end before block start is impossible at any scale.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>PCM-D-10, PREP-09</t>
+          <t>PREP-09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>No action. PREP-08 deliberately excludes them from nulling -- protection was correct in principle and moot in practice.</t>
+          <t>Genuine error. Decide whether to null it or report upstream. Only one row.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Emergent</t>
+          <t>rt_ADMIT_to_* family</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>RESOLVED-KEEP</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7 in md1, 21 in md8</t>
+          <t>1-4 each</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.05% and 0.09% positive at source, with matching blank shares across two independent exports. Consistent with a field clinicians rarely complete rather than a true emergency rate.</t>
+          <t>Small negative counts. Plausibly real (a block placed in pre-op before the formal admit timestamp) or plausibly error at these counts.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>PCM-F-06, PCM-D-04</t>
+          <t>PREP-09</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>RETAINED with a caveat. The merged value is md3-owned; see qc/06_reconcile_summary.txt for the observed distribution. Do NOT model on it without checking Patient_Type and Admit_Source first.</t>
+          <t>Review the PREP-09 report. Low volume either way.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>rt_ANCHOR_to_ADMIT_days etc.</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED-KEEP</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Zero negatives found. These are offsets from an anchor date where negative would be LEGITIMATE.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>PCM-D-10, PREP-09</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No action. PREP-08 deliberately excludes them from nulling -- protection was correct in principle and moot in practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Emergent</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED-KEEP</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>7 in md1, 21 in md8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.05% and 0.09% positive at source, with matching blank shares across two independent exports. Consistent with a field clinicians rarely complete rather than a true emergency rate.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>PCM-F-06, PCM-D-04</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>RETAINED with a caveat. The merged value is md3-owned; see qc/06_reconcile_summary.txt for the observed distribution. Do NOT model on it without checking Patient_Type and Admit_Source first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Intraop_Ketamine, Preop_block</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>RESOLVED-KEEP</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Y-or-blank in every source -- no explicit N anywhere. Blank means 'not given', not 'unknown'.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>PCM-F-06</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Derive explicit 0/1 indicators downstream rather than leaving a variable that is never N.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/VARIABLE_RECTIFICATION.xlsx
+++ b/docs/VARIABLE_RECTIFICATION.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KEY'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KEY'!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Duplicate Concepts'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Type &amp; Encoding'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Quality'!$A$1:$G$13</definedName>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -629,29 +629,41 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Sheets</t>
+          <t>Phase 10</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Concepts | Type &amp; Encoding | Data Quality | Coverage &amp; Cohort | Traps</t>
+          <t>Rows marked VERIFY on the Duplicate Concepts sheet are answered by Phase 10. 10_concept_profile.sas writes the value evidence and a decision template; 10b_concept_harmonize.sas applies only what a human confirms, into new h_ columns, leaving every original column untouched.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate Concepts | Type &amp; Encoding | Data Quality | Coverage &amp; Cohort | Traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Caution</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>This register is the project's accumulated knowledge, not a substitute for inspecting the data. Where a row says VERIFY, the check has NOT been run.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
+  <autoFilter ref="A1:B16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -744,7 +756,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Kept as three columns. Any mortality analysis must decide which applies to which patients -- in_md1..in_md8 make that determinable. Record in the data dictionary.</t>
+          <t>Kept as three columns. Profiled by Phase 10 under concept DEATH_FLAG -- the Cross-Tabs sheet shows whether they agree where they co-occur. If confirmed, 10b builds a single standardized column and leaves all three originals intact.</t>
         </is>
       </c>
     </row>
@@ -966,7 +978,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Kept. VERIFY whether the numeric and character forms encode the same thing before using either.</t>
+          <t>Kept. VERIFY via Phase 10 -- the five char/numeric pairs are profiled as FRAILTY_EXHAUST, FRAILTY_ACTIVITY, FRAILTY_WALKING, FRAILTY_WEIGHT and FRAILTY_GRIP.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1015,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>VERIFY: cross-tab against the md4 column on overlapping patients. If they agree, one column is redundant.</t>
+          <t>VERIFY via Phase 10 -- profiled under concept ISO_SEV_AVERAGE. Note md8 ISO_SEV_MAC_TOTAL_Exp is deliberately EXCLUDED from that group: it is a TOTAL, not an average.</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1126,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>VERIFY: compare on overlapping patients. If identical, collapse to one column and document.</t>
+          <t>VERIFY via Phase 10: 10_concept_profile.sas cross-tabulates the pair and writes the evidence to docs/CONCEPT_EVIDENCE.xlsx. Confirm in concept_decisions.csv, then 10b_concept_harmonize.sas builds the standardized column.</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1348,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>VERIFY: proc freq Cognitive_Score * Cognitive_Category / list missing. A clean one-to-many mapping means Category is derivable and redundant.</t>
+          <t>VERIFY via Phase 10 -- profiled under concept COGNITIVE_GRAIN. A clean one-to-many mapping in the Cross-Tabs sheet means Category is derivable from Score and one column is redundant.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1385,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>VERIFY: proc freq Frailty_Score * Frailty_Category / list missing.</t>
+          <t>VERIFY via Phase 10 -- profiled under concept FRAILTY_GRAIN.</t>
         </is>
       </c>
     </row>
